--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -4019,10 +4019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120835815</v>
+        <v>120835614</v>
       </c>
       <c r="B34" t="n">
-        <v>91998</v>
+        <v>8432</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563484</v>
+        <v>563522</v>
       </c>
       <c r="R34" t="n">
-        <v>6515764</v>
+        <v>6515762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120835614</v>
+        <v>120835611</v>
       </c>
       <c r="B35" t="n">
-        <v>8432</v>
+        <v>78243</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4133,25 +4133,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120835611</v>
+        <v>120835815</v>
       </c>
       <c r="B36" t="n">
-        <v>78243</v>
+        <v>91998</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4239,21 +4239,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563522</v>
+        <v>563484</v>
       </c>
       <c r="R36" t="n">
-        <v>6515762</v>
+        <v>6515764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4631,10 +4631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120836006</v>
+        <v>120835770</v>
       </c>
       <c r="B40" t="n">
-        <v>79216</v>
+        <v>91998</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4647,37 +4647,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563357</v>
+        <v>563522</v>
       </c>
       <c r="R40" t="n">
-        <v>6515821</v>
+        <v>6515762</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4721,22 +4721,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120835770</v>
+        <v>120836006</v>
       </c>
       <c r="B41" t="n">
-        <v>91998</v>
+        <v>79216</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4749,37 +4749,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563522</v>
+        <v>563357</v>
       </c>
       <c r="R41" t="n">
-        <v>6515762</v>
+        <v>6515821</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4823,12 +4823,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120894013</v>
+        <v>120895554</v>
       </c>
       <c r="B53" t="n">
-        <v>78243</v>
+        <v>79216</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5973,34 +5973,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563039</v>
+        <v>563179</v>
       </c>
       <c r="R53" t="n">
-        <v>6515310</v>
+        <v>6515532</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6059,10 +6059,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120895554</v>
+        <v>120894013</v>
       </c>
       <c r="B54" t="n">
-        <v>79216</v>
+        <v>78243</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6075,34 +6075,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563179</v>
+        <v>563039</v>
       </c>
       <c r="R54" t="n">
-        <v>6515532</v>
+        <v>6515310</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -3713,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120836410</v>
+        <v>120835744</v>
       </c>
       <c r="B31" t="n">
-        <v>79216</v>
+        <v>91973</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3725,38 +3725,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563390</v>
+        <v>563520</v>
       </c>
       <c r="R31" t="n">
-        <v>6515758</v>
+        <v>6515747</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120835808</v>
+        <v>120835473</v>
       </c>
       <c r="B32" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563484</v>
+        <v>563532</v>
       </c>
       <c r="R32" t="n">
-        <v>6515764</v>
+        <v>6515728</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3905,22 +3905,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120835487</v>
+        <v>120836018</v>
       </c>
       <c r="B33" t="n">
-        <v>90707</v>
+        <v>92008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3933,37 +3933,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563532</v>
+        <v>563484</v>
       </c>
       <c r="R33" t="n">
-        <v>6515728</v>
+        <v>6515764</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4007,22 +4007,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120835614</v>
+        <v>120836109</v>
       </c>
       <c r="B34" t="n">
-        <v>8432</v>
+        <v>94747</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4035,37 +4035,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563522</v>
+        <v>563408</v>
       </c>
       <c r="R34" t="n">
-        <v>6515762</v>
+        <v>6515763</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4124,7 +4124,7 @@
         <v>120835611</v>
       </c>
       <c r="B35" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120835815</v>
+        <v>120835774</v>
       </c>
       <c r="B36" t="n">
-        <v>91998</v>
+        <v>78246</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563484</v>
+        <v>563520</v>
       </c>
       <c r="R36" t="n">
-        <v>6515764</v>
+        <v>6515747</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4313,22 +4313,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120835916</v>
+        <v>120836006</v>
       </c>
       <c r="B37" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4337,38 +4337,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563423</v>
+        <v>563357</v>
       </c>
       <c r="R37" t="n">
-        <v>6515833</v>
+        <v>6515821</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120836116</v>
+        <v>120835609</v>
       </c>
       <c r="B38" t="n">
-        <v>78243</v>
+        <v>79219</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,37 +4443,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563408</v>
+        <v>563522</v>
       </c>
       <c r="R38" t="n">
-        <v>6515763</v>
+        <v>6515762</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4517,22 +4517,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120835860</v>
+        <v>120836410</v>
       </c>
       <c r="B39" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,14 +4565,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563423</v>
+        <v>563390</v>
       </c>
       <c r="R39" t="n">
-        <v>6515833</v>
+        <v>6515758</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4634,7 +4634,7 @@
         <v>120835770</v>
       </c>
       <c r="B40" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4733,10 +4733,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120836006</v>
+        <v>120835860</v>
       </c>
       <c r="B41" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4769,14 +4769,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563357</v>
+        <v>563423</v>
       </c>
       <c r="R41" t="n">
-        <v>6515821</v>
+        <v>6515833</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120836502</v>
+        <v>120835487</v>
       </c>
       <c r="B42" t="n">
-        <v>91998</v>
+        <v>90717</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4851,37 +4851,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563345</v>
+        <v>563532</v>
       </c>
       <c r="R42" t="n">
-        <v>6515843</v>
+        <v>6515728</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4925,22 +4925,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120835774</v>
+        <v>120836502</v>
       </c>
       <c r="B43" t="n">
-        <v>78243</v>
+        <v>92008</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4953,37 +4953,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563520</v>
+        <v>563345</v>
       </c>
       <c r="R43" t="n">
-        <v>6515747</v>
+        <v>6515843</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5027,22 +5027,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120835744</v>
+        <v>120836116</v>
       </c>
       <c r="B44" t="n">
-        <v>91963</v>
+        <v>78246</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5051,25 +5051,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563520</v>
+        <v>563408</v>
       </c>
       <c r="R44" t="n">
-        <v>6515747</v>
+        <v>6515763</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5141,10 +5141,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120835609</v>
+        <v>120835614</v>
       </c>
       <c r="B45" t="n">
-        <v>79216</v>
+        <v>8432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5153,25 +5153,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120836109</v>
+        <v>120835916</v>
       </c>
       <c r="B46" t="n">
-        <v>94737</v>
+        <v>8432</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563408</v>
+        <v>563423</v>
       </c>
       <c r="R46" t="n">
-        <v>6515763</v>
+        <v>6515833</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120836503</v>
+        <v>120835808</v>
       </c>
       <c r="B47" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5381,17 +5381,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563342</v>
+        <v>563484</v>
       </c>
       <c r="R47" t="n">
-        <v>6515842</v>
+        <v>6515764</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5435,22 +5435,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120835473</v>
+        <v>120836503</v>
       </c>
       <c r="B48" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5483,14 +5483,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563532</v>
+        <v>563342</v>
       </c>
       <c r="R48" t="n">
-        <v>6515728</v>
+        <v>6515842</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120893897</v>
+        <v>120893985</v>
       </c>
       <c r="B49" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563080</v>
+        <v>563068</v>
       </c>
       <c r="R49" t="n">
-        <v>6515376</v>
+        <v>6515304</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120893999</v>
+        <v>120895747</v>
       </c>
       <c r="B50" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5687,14 +5687,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563068</v>
+        <v>563272</v>
       </c>
       <c r="R50" t="n">
-        <v>6515304</v>
+        <v>6515573</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -5756,7 +5756,7 @@
         <v>120893971</v>
       </c>
       <c r="B51" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120893921</v>
+        <v>120893893</v>
       </c>
       <c r="B52" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5867,25 +5867,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563089</v>
+        <v>563080</v>
       </c>
       <c r="R52" t="n">
-        <v>6515313</v>
+        <v>6515376</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120895554</v>
+        <v>120895700</v>
       </c>
       <c r="B53" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5997,10 +5997,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563179</v>
+        <v>563209</v>
       </c>
       <c r="R53" t="n">
-        <v>6515532</v>
+        <v>6515543</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6059,10 +6059,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120894013</v>
+        <v>120893921</v>
       </c>
       <c r="B54" t="n">
-        <v>78243</v>
+        <v>8432</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6071,25 +6071,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563039</v>
+        <v>563089</v>
       </c>
       <c r="R54" t="n">
-        <v>6515310</v>
+        <v>6515313</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6268,10 +6268,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120895747</v>
+        <v>120895554</v>
       </c>
       <c r="B56" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6308,10 +6308,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563272</v>
+        <v>563179</v>
       </c>
       <c r="R56" t="n">
-        <v>6515573</v>
+        <v>6515532</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6370,10 +6370,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120895700</v>
+        <v>120894013</v>
       </c>
       <c r="B57" t="n">
-        <v>79216</v>
+        <v>78246</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6386,34 +6386,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563209</v>
+        <v>563039</v>
       </c>
       <c r="R57" t="n">
-        <v>6515543</v>
+        <v>6515310</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -5549,7 +5549,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120893985</v>
+        <v>120895554</v>
       </c>
       <c r="B49" t="n">
         <v>79219</v>
@@ -5585,14 +5585,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563068</v>
+        <v>563179</v>
       </c>
       <c r="R49" t="n">
-        <v>6515304</v>
+        <v>6515532</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120895747</v>
+        <v>120893999</v>
       </c>
       <c r="B50" t="n">
         <v>79219</v>
@@ -5687,14 +5687,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563272</v>
+        <v>563068</v>
       </c>
       <c r="R50" t="n">
-        <v>6515573</v>
+        <v>6515304</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120893971</v>
+        <v>120895747</v>
       </c>
       <c r="B51" t="n">
         <v>79219</v>
@@ -5789,14 +5789,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563064</v>
+        <v>563272</v>
       </c>
       <c r="R51" t="n">
-        <v>6515295</v>
+        <v>6515573</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120895700</v>
+        <v>120896019</v>
       </c>
       <c r="B53" t="n">
-        <v>79219</v>
+        <v>5169</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5969,38 +5969,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563209</v>
+        <v>563374</v>
       </c>
       <c r="R53" t="n">
-        <v>6515543</v>
+        <v>6515412</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6059,10 +6064,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120893921</v>
+        <v>120893971</v>
       </c>
       <c r="B54" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6071,25 +6076,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6099,13 +6104,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563089</v>
+        <v>563064</v>
       </c>
       <c r="R54" t="n">
-        <v>6515313</v>
+        <v>6515295</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6161,10 +6166,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120896019</v>
+        <v>120895700</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>79219</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6173,43 +6178,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563374</v>
+        <v>563209</v>
       </c>
       <c r="R55" t="n">
-        <v>6515412</v>
+        <v>6515543</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6268,10 +6268,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120895554</v>
+        <v>120894013</v>
       </c>
       <c r="B56" t="n">
-        <v>79219</v>
+        <v>78246</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6284,34 +6284,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563179</v>
+        <v>563039</v>
       </c>
       <c r="R56" t="n">
-        <v>6515532</v>
+        <v>6515310</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6370,10 +6370,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120894013</v>
+        <v>120893921</v>
       </c>
       <c r="B57" t="n">
-        <v>78246</v>
+        <v>8432</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6382,25 +6382,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563039</v>
+        <v>563089</v>
       </c>
       <c r="R57" t="n">
-        <v>6515310</v>
+        <v>6515313</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6166,10 +6166,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120895700</v>
+        <v>120894013</v>
       </c>
       <c r="B55" t="n">
-        <v>79219</v>
+        <v>78246</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6182,34 +6182,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563209</v>
+        <v>563039</v>
       </c>
       <c r="R55" t="n">
-        <v>6515543</v>
+        <v>6515310</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6268,10 +6268,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120894013</v>
+        <v>120895700</v>
       </c>
       <c r="B56" t="n">
-        <v>78246</v>
+        <v>79219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6284,34 +6284,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563039</v>
+        <v>563209</v>
       </c>
       <c r="R56" t="n">
-        <v>6515310</v>
+        <v>6515543</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6470,6 +6470,2182 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131740615</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>563087</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6515384</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Klenare granlåga</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131739161</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>563295</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6515614</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131739160</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>563430</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6515631</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131732595</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78926</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>353</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>563194</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6515482</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131737947</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>563453</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6515693</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131737948</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>563371</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6515533</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131737951</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>563084</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6515314</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Relativt färska i tallåga</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131732596</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78926</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>353</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>563156</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6515417</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131733192</v>
+      </c>
+      <c r="B66" t="n">
+        <v>96624</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>563407</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6515612</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I hänsyn. Större kuddar.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131739165</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>563099</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6515316</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Död ved av tall under ledning</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131732593</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78926</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>353</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>563411</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6515751</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131732852</v>
+      </c>
+      <c r="B69" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>563493</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6515767</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131732854</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>563365</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6515579</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131739159</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>563405</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6515760</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131739158</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Långåsarna Sydost, Ög</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>563359</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6515817</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131739166</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>563082</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6515367</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På lump</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131739164</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>563123</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6515351</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Gammal ihålig avverkningsstubbe av tall</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131739162</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>563176</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6515462</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131737950</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>563288</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6515549</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131739163</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>563123</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6515409</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131737949</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>563333</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6515510</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B60" t="n">
-        <v>79879</v>
+        <v>78926</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R60" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,11 +6750,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6785,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B61" t="n">
-        <v>78926</v>
+        <v>79879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6796,34 +6791,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R61" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6851,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,45 +7199,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131732596</v>
+        <v>131733192</v>
       </c>
       <c r="B65" t="n">
-        <v>78926</v>
+        <v>96624</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563156</v>
+        <v>563407</v>
       </c>
       <c r="R65" t="n">
-        <v>6515417</v>
+        <v>6515612</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>I hänsyn. Större kuddar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,45 +7305,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131733192</v>
+        <v>131732596</v>
       </c>
       <c r="B66" t="n">
-        <v>96624</v>
+        <v>78926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563407</v>
+        <v>563156</v>
       </c>
       <c r="R66" t="n">
-        <v>6515612</v>
+        <v>6515417</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>I hänsyn. Större kuddar.</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8446,45 +8446,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131739163</v>
+        <v>131737949</v>
       </c>
       <c r="B77" t="n">
-        <v>79879</v>
+        <v>8453</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563123</v>
+        <v>563333</v>
       </c>
       <c r="R77" t="n">
-        <v>6515409</v>
+        <v>6515510</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8547,45 +8547,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737949</v>
+        <v>131739163</v>
       </c>
       <c r="B78" t="n">
-        <v>8453</v>
+        <v>79879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563333</v>
+        <v>563123</v>
       </c>
       <c r="R78" t="n">
-        <v>6515510</v>
+        <v>6515409</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6475,7 +6475,7 @@
         <v>131740615</v>
       </c>
       <c r="B58" t="n">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>131739161</v>
       </c>
       <c r="B59" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>131732595</v>
       </c>
       <c r="B60" t="n">
-        <v>78926</v>
+        <v>78927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>131739160</v>
       </c>
       <c r="B61" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>131737947</v>
       </c>
       <c r="B62" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>131737948</v>
       </c>
       <c r="B63" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>131737951</v>
       </c>
       <c r="B64" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7199,45 +7199,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131733192</v>
+        <v>131739165</v>
       </c>
       <c r="B65" t="n">
-        <v>96624</v>
+        <v>79880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563407</v>
+        <v>563099</v>
       </c>
       <c r="R65" t="n">
-        <v>6515612</v>
+        <v>6515316</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I hänsyn. Större kuddar.</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,45 +7305,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131732596</v>
+        <v>131733192</v>
       </c>
       <c r="B66" t="n">
-        <v>78926</v>
+        <v>96625</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563156</v>
+        <v>563407</v>
       </c>
       <c r="R66" t="n">
-        <v>6515417</v>
+        <v>6515612</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>I hänsyn. Större kuddar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B67" t="n">
-        <v>79879</v>
+        <v>78927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R67" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7520,7 +7520,7 @@
         <v>131732593</v>
       </c>
       <c r="B68" t="n">
-        <v>78926</v>
+        <v>78927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>131732852</v>
       </c>
       <c r="B69" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>131732854</v>
       </c>
       <c r="B70" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7820,10 +7820,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131739159</v>
+        <v>131739158</v>
       </c>
       <c r="B71" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7851,14 +7851,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Sydost, Ög</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>563405</v>
+        <v>563359</v>
       </c>
       <c r="R71" t="n">
-        <v>6515760</v>
+        <v>6515817</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7921,10 +7921,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739158</v>
+        <v>131739159</v>
       </c>
       <c r="B72" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7952,14 +7952,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långåsarna Sydost, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563359</v>
+        <v>563405</v>
       </c>
       <c r="R72" t="n">
-        <v>6515817</v>
+        <v>6515760</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8025,7 +8025,7 @@
         <v>131739166</v>
       </c>
       <c r="B73" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>131739164</v>
       </c>
       <c r="B74" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>131739162</v>
       </c>
       <c r="B75" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>131737950</v>
       </c>
       <c r="B76" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8446,45 +8446,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737949</v>
+        <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>8453</v>
+        <v>79880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563333</v>
+        <v>563123</v>
       </c>
       <c r="R77" t="n">
-        <v>6515510</v>
+        <v>6515409</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8547,45 +8547,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739163</v>
+        <v>131737949</v>
       </c>
       <c r="B78" t="n">
-        <v>79879</v>
+        <v>8454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563123</v>
+        <v>563333</v>
       </c>
       <c r="R78" t="n">
-        <v>6515409</v>
+        <v>6515510</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6581,7 +6581,7 @@
         <v>131739161</v>
       </c>
       <c r="B59" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B60" t="n">
-        <v>78927</v>
+        <v>79883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R60" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,6 +6750,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6780,10 +6785,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B61" t="n">
-        <v>79880</v>
+        <v>78930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6791,34 +6796,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R61" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6851,11 +6856,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,10 +7199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B65" t="n">
-        <v>79880</v>
+        <v>78930</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7210,21 +7210,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R65" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7308,7 +7308,7 @@
         <v>131733192</v>
       </c>
       <c r="B66" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131732596</v>
+        <v>131739165</v>
       </c>
       <c r="B67" t="n">
-        <v>78927</v>
+        <v>79883</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563156</v>
+        <v>563099</v>
       </c>
       <c r="R67" t="n">
-        <v>6515417</v>
+        <v>6515316</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7520,7 +7520,7 @@
         <v>131732593</v>
       </c>
       <c r="B68" t="n">
-        <v>78927</v>
+        <v>78930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>131732852</v>
       </c>
       <c r="B69" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>131732854</v>
       </c>
       <c r="B70" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>131739158</v>
       </c>
       <c r="B71" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>131739159</v>
       </c>
       <c r="B72" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>131739166</v>
       </c>
       <c r="B73" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>131739164</v>
       </c>
       <c r="B74" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>131739162</v>
       </c>
       <c r="B75" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -7199,45 +7199,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131732596</v>
+        <v>131733192</v>
       </c>
       <c r="B65" t="n">
-        <v>78930</v>
+        <v>96628</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563156</v>
+        <v>563407</v>
       </c>
       <c r="R65" t="n">
-        <v>6515417</v>
+        <v>6515612</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>I hänsyn. Större kuddar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,45 +7305,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131733192</v>
+        <v>131739165</v>
       </c>
       <c r="B66" t="n">
-        <v>96628</v>
+        <v>79883</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563407</v>
+        <v>563099</v>
       </c>
       <c r="R66" t="n">
-        <v>6515612</v>
+        <v>6515316</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>I hänsyn. Större kuddar.</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B67" t="n">
-        <v>79883</v>
+        <v>78930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R67" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7820,7 +7820,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131739158</v>
+        <v>131739159</v>
       </c>
       <c r="B71" t="n">
         <v>79883</v>
@@ -7851,14 +7851,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långåsarna Sydost, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>563359</v>
+        <v>563405</v>
       </c>
       <c r="R71" t="n">
-        <v>6515817</v>
+        <v>6515760</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739159</v>
+        <v>131739158</v>
       </c>
       <c r="B72" t="n">
         <v>79883</v>
@@ -7952,14 +7952,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Sydost, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563405</v>
+        <v>563359</v>
       </c>
       <c r="R72" t="n">
-        <v>6515760</v>
+        <v>6515817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8446,45 +8446,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131739163</v>
+        <v>131737949</v>
       </c>
       <c r="B77" t="n">
-        <v>79883</v>
+        <v>8454</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563123</v>
+        <v>563333</v>
       </c>
       <c r="R77" t="n">
-        <v>6515409</v>
+        <v>6515510</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8547,45 +8547,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737949</v>
+        <v>131739163</v>
       </c>
       <c r="B78" t="n">
-        <v>8454</v>
+        <v>79883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563333</v>
+        <v>563123</v>
       </c>
       <c r="R78" t="n">
-        <v>6515510</v>
+        <v>6515409</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B60" t="n">
-        <v>79883</v>
+        <v>78930</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R60" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,11 +6750,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6785,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B61" t="n">
-        <v>78930</v>
+        <v>79883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6796,34 +6791,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R61" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6851,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7305,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B66" t="n">
-        <v>79883</v>
+        <v>78930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R66" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131732596</v>
+        <v>131739165</v>
       </c>
       <c r="B67" t="n">
-        <v>78930</v>
+        <v>79883</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563156</v>
+        <v>563099</v>
       </c>
       <c r="R67" t="n">
-        <v>6515417</v>
+        <v>6515316</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8446,45 +8446,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737949</v>
+        <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>8454</v>
+        <v>79883</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563333</v>
+        <v>563123</v>
       </c>
       <c r="R77" t="n">
-        <v>6515510</v>
+        <v>6515409</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8547,45 +8547,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739163</v>
+        <v>131737949</v>
       </c>
       <c r="B78" t="n">
-        <v>79883</v>
+        <v>8454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563123</v>
+        <v>563333</v>
       </c>
       <c r="R78" t="n">
-        <v>6515409</v>
+        <v>6515510</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B60" t="n">
-        <v>78930</v>
+        <v>79883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R60" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,6 +6750,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6780,10 +6785,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B61" t="n">
-        <v>79883</v>
+        <v>78930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6791,34 +6796,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R61" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6851,11 +6856,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6581,7 +6581,7 @@
         <v>131739161</v>
       </c>
       <c r="B59" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B60" t="n">
-        <v>79883</v>
+        <v>78932</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R60" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,11 +6750,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6785,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B61" t="n">
-        <v>78930</v>
+        <v>79885</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6796,34 +6791,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R61" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6851,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6886,7 +6886,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737947</v>
+        <v>131737951</v>
       </c>
       <c r="B62" t="n">
         <v>8454</v>
@@ -6917,14 +6917,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563453</v>
+        <v>563084</v>
       </c>
       <c r="R62" t="n">
-        <v>6515693</v>
+        <v>6515314</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,6 +6957,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Relativt färska i tallåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7093,7 +7098,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737951</v>
+        <v>131737947</v>
       </c>
       <c r="B64" t="n">
         <v>8454</v>
@@ -7124,14 +7129,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563084</v>
+        <v>563453</v>
       </c>
       <c r="R64" t="n">
-        <v>6515314</v>
+        <v>6515693</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,11 +7169,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Relativt färska i tallåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7202,7 +7202,7 @@
         <v>131733192</v>
       </c>
       <c r="B65" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>131732596</v>
       </c>
       <c r="B66" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>131739165</v>
       </c>
       <c r="B67" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>131732593</v>
       </c>
       <c r="B68" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131732852</v>
+        <v>131732854</v>
       </c>
       <c r="B69" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7649,14 +7649,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563493</v>
+        <v>563365</v>
       </c>
       <c r="R69" t="n">
-        <v>6515767</v>
+        <v>6515579</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7719,10 +7719,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131732854</v>
+        <v>131732852</v>
       </c>
       <c r="B70" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7750,14 +7750,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563365</v>
+        <v>563493</v>
       </c>
       <c r="R70" t="n">
-        <v>6515579</v>
+        <v>6515767</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7823,7 +7823,7 @@
         <v>131739159</v>
       </c>
       <c r="B71" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>131739158</v>
       </c>
       <c r="B72" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>131739166</v>
       </c>
       <c r="B73" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>131739164</v>
       </c>
       <c r="B74" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>131739162</v>
       </c>
       <c r="B75" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -7305,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131732596</v>
+        <v>131739165</v>
       </c>
       <c r="B66" t="n">
-        <v>78932</v>
+        <v>79885</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563156</v>
+        <v>563099</v>
       </c>
       <c r="R66" t="n">
-        <v>6515417</v>
+        <v>6515316</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B67" t="n">
-        <v>79885</v>
+        <v>78932</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R67" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -7305,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B66" t="n">
-        <v>79885</v>
+        <v>78932</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R66" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131732596</v>
+        <v>131739165</v>
       </c>
       <c r="B67" t="n">
-        <v>78932</v>
+        <v>79885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563156</v>
+        <v>563099</v>
       </c>
       <c r="R67" t="n">
-        <v>6515417</v>
+        <v>6515316</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6475,7 +6475,7 @@
         <v>131740615</v>
       </c>
       <c r="B58" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>131739161</v>
       </c>
       <c r="B59" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B60" t="n">
-        <v>78932</v>
+        <v>79888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R60" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,6 +6750,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6780,10 +6785,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B61" t="n">
-        <v>79885</v>
+        <v>78935</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6791,34 +6796,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R61" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6851,11 +6856,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6886,10 +6886,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737951</v>
+        <v>131737947</v>
       </c>
       <c r="B62" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,14 +6917,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563084</v>
+        <v>563453</v>
       </c>
       <c r="R62" t="n">
-        <v>6515314</v>
+        <v>6515693</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,11 +6957,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Relativt färska i tallåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6995,7 +6990,7 @@
         <v>131737948</v>
       </c>
       <c r="B63" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7098,10 +7093,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737947</v>
+        <v>131737951</v>
       </c>
       <c r="B64" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7129,14 +7124,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563453</v>
+        <v>563084</v>
       </c>
       <c r="R64" t="n">
-        <v>6515693</v>
+        <v>6515314</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7169,6 +7164,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Relativt färska i tallåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7202,7 +7202,7 @@
         <v>131733192</v>
       </c>
       <c r="B65" t="n">
-        <v>96634</v>
+        <v>96637</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131732596</v>
+        <v>131739165</v>
       </c>
       <c r="B66" t="n">
-        <v>78932</v>
+        <v>79888</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563156</v>
+        <v>563099</v>
       </c>
       <c r="R66" t="n">
-        <v>6515417</v>
+        <v>6515316</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B67" t="n">
-        <v>79885</v>
+        <v>78935</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R67" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7520,7 +7520,7 @@
         <v>131732593</v>
       </c>
       <c r="B68" t="n">
-        <v>78932</v>
+        <v>78935</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131732854</v>
+        <v>131732852</v>
       </c>
       <c r="B69" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7649,14 +7649,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563365</v>
+        <v>563493</v>
       </c>
       <c r="R69" t="n">
-        <v>6515579</v>
+        <v>6515767</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7719,10 +7719,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131732852</v>
+        <v>131732854</v>
       </c>
       <c r="B70" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7750,14 +7750,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563493</v>
+        <v>563365</v>
       </c>
       <c r="R70" t="n">
-        <v>6515767</v>
+        <v>6515579</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7823,7 +7823,7 @@
         <v>131739159</v>
       </c>
       <c r="B71" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>131739158</v>
       </c>
       <c r="B72" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>131739166</v>
       </c>
       <c r="B73" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>131739164</v>
       </c>
       <c r="B74" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>131739162</v>
       </c>
       <c r="B75" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>131737950</v>
       </c>
       <c r="B76" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>131737949</v>
       </c>
       <c r="B78" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6581,7 +6581,7 @@
         <v>131739161</v>
       </c>
       <c r="B59" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>131739160</v>
       </c>
       <c r="B60" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>131732595</v>
       </c>
       <c r="B61" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>131733192</v>
       </c>
       <c r="B65" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>131739165</v>
       </c>
       <c r="B66" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>131732596</v>
       </c>
       <c r="B67" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>131732593</v>
       </c>
       <c r="B68" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>131732852</v>
       </c>
       <c r="B69" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>131732854</v>
       </c>
       <c r="B70" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>131739159</v>
       </c>
       <c r="B71" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>131739158</v>
       </c>
       <c r="B72" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>131739166</v>
       </c>
       <c r="B73" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>131739164</v>
       </c>
       <c r="B74" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>131739162</v>
       </c>
       <c r="B75" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B60" t="n">
-        <v>79893</v>
+        <v>78940</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R60" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,11 +6750,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6785,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B61" t="n">
-        <v>78940</v>
+        <v>79893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6796,34 +6791,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R61" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6851,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,45 +7199,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131733192</v>
+        <v>131732596</v>
       </c>
       <c r="B65" t="n">
-        <v>96642</v>
+        <v>78940</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563407</v>
+        <v>563156</v>
       </c>
       <c r="R65" t="n">
-        <v>6515612</v>
+        <v>6515417</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I hänsyn. Större kuddar.</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,45 +7305,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131739165</v>
+        <v>131733192</v>
       </c>
       <c r="B66" t="n">
-        <v>79893</v>
+        <v>96642</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563099</v>
+        <v>563407</v>
       </c>
       <c r="R66" t="n">
-        <v>6515316</v>
+        <v>6515612</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>I hänsyn. Större kuddar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131732596</v>
+        <v>131739165</v>
       </c>
       <c r="B67" t="n">
-        <v>78940</v>
+        <v>79893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563156</v>
+        <v>563099</v>
       </c>
       <c r="R67" t="n">
-        <v>6515417</v>
+        <v>6515316</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -6581,7 +6581,7 @@
         <v>131739161</v>
       </c>
       <c r="B59" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739160</v>
+        <v>131732595</v>
       </c>
       <c r="B60" t="n">
-        <v>79934</v>
+        <v>78983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563430</v>
+        <v>563194</v>
       </c>
       <c r="R60" t="n">
-        <v>6515631</v>
+        <v>6515482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,11 +6750,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6785,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131732595</v>
+        <v>131739160</v>
       </c>
       <c r="B61" t="n">
-        <v>78981</v>
+        <v>79936</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6796,34 +6791,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563194</v>
+        <v>563430</v>
       </c>
       <c r="R61" t="n">
-        <v>6515482</v>
+        <v>6515631</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6851,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,45 +7199,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131733192</v>
+        <v>131739165</v>
       </c>
       <c r="B65" t="n">
-        <v>96685</v>
+        <v>79936</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563407</v>
+        <v>563099</v>
       </c>
       <c r="R65" t="n">
-        <v>6515612</v>
+        <v>6515316</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I hänsyn. Större kuddar.</t>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,45 +7305,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131732596</v>
+        <v>131733192</v>
       </c>
       <c r="B66" t="n">
-        <v>78981</v>
+        <v>96688</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563156</v>
+        <v>563407</v>
       </c>
       <c r="R66" t="n">
-        <v>6515417</v>
+        <v>6515612</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>I hänsyn. Större kuddar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739165</v>
+        <v>131732596</v>
       </c>
       <c r="B67" t="n">
-        <v>79934</v>
+        <v>78983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563099</v>
+        <v>563156</v>
       </c>
       <c r="R67" t="n">
-        <v>6515316</v>
+        <v>6515417</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Död ved av tall under ledning</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7520,7 +7520,7 @@
         <v>131732593</v>
       </c>
       <c r="B68" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>131732852</v>
       </c>
       <c r="B69" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>131732854</v>
       </c>
       <c r="B70" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>131739159</v>
       </c>
       <c r="B71" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>131739158</v>
       </c>
       <c r="B72" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>131739166</v>
       </c>
       <c r="B73" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>131739164</v>
       </c>
       <c r="B74" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>131739162</v>
       </c>
       <c r="B75" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8446,45 +8446,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737949</v>
+        <v>131739163</v>
       </c>
       <c r="B77" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563333</v>
+        <v>563123</v>
       </c>
       <c r="R77" t="n">
-        <v>6515510</v>
+        <v>6515409</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8547,45 +8547,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739163</v>
+        <v>131737949</v>
       </c>
       <c r="B78" t="n">
-        <v>79934</v>
+        <v>8455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563123</v>
+        <v>563333</v>
       </c>
       <c r="R78" t="n">
-        <v>6515409</v>
+        <v>6515510</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92007211</v>
+        <v>120682796</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563447.9274969376</v>
+        <v>563454</v>
       </c>
       <c r="R2" t="n">
-        <v>6515469.968933116</v>
+        <v>6515486</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Holmen</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92007210</v>
+        <v>120683046</v>
       </c>
       <c r="B3" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,40 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563391.8188633039</v>
+        <v>563434</v>
       </c>
       <c r="R3" t="n">
-        <v>6515437.932580597</v>
+        <v>6515522</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,38 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Holmen</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97569053</v>
+        <v>120683502</v>
       </c>
       <c r="B4" t="n">
-        <v>4932</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100515</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronspraktbagge</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buprestis haemorrhoidalis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Herbst, 1780</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klintaberget/Skybygget, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563274.6925021718</v>
+        <v>563290</v>
       </c>
       <c r="R4" t="n">
-        <v>6515547.003421308</v>
+        <v>6515611</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Håkansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97569033</v>
+        <v>120683922</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klintaberget/Skybygget, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563411.6133904945</v>
+        <v>563452</v>
       </c>
       <c r="R5" t="n">
-        <v>6515688.747886149</v>
+        <v>6515685</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Håkansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105311995</v>
+        <v>120835611</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563410.8937009784</v>
+        <v>563522</v>
       </c>
       <c r="R6" t="n">
-        <v>6515605.759390441</v>
+        <v>6515762</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,58 +1144,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sanna Strömberg </t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanna Strömberg </t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120683660</v>
+        <v>120835774</v>
       </c>
       <c r="B7" t="n">
-        <v>94829</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563407</v>
+        <v>563520</v>
       </c>
       <c r="R7" t="n">
-        <v>6515610</v>
+        <v>6515747</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1322,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120683991</v>
+        <v>120836116</v>
       </c>
       <c r="B8" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563452</v>
+        <v>563408</v>
       </c>
       <c r="R8" t="n">
-        <v>6515685</v>
+        <v>6515763</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1424,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120682796</v>
+        <v>120894013</v>
       </c>
       <c r="B9" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563454</v>
+        <v>563039</v>
       </c>
       <c r="R9" t="n">
-        <v>6515486</v>
+        <v>6515310</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1526,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120684460</v>
+        <v>131732593</v>
       </c>
       <c r="B10" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563462</v>
+        <v>563411</v>
       </c>
       <c r="R10" t="n">
-        <v>6515641</v>
+        <v>6515751</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,27 +1536,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120683599</v>
+        <v>131732595</v>
       </c>
       <c r="B11" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,37 +1563,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563349</v>
+        <v>563194</v>
       </c>
       <c r="R11" t="n">
-        <v>6515633</v>
+        <v>6515482</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,12 +1617,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,27 +1637,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120683056</v>
+        <v>131732596</v>
       </c>
       <c r="B12" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,37 +1664,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563434</v>
+        <v>563156</v>
       </c>
       <c r="R12" t="n">
-        <v>6515522</v>
+        <v>6515417</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1832,12 +1718,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,49 +1743,48 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120682748</v>
+        <v>120836109</v>
       </c>
       <c r="B13" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1904,10 +1794,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563472</v>
+        <v>563408</v>
       </c>
       <c r="R13" t="n">
-        <v>6515480</v>
+        <v>6515763</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1934,12 +1824,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,37 +1856,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120683838</v>
+        <v>120683660</v>
       </c>
       <c r="B14" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2006,10 +1891,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563506</v>
+        <v>563407</v>
       </c>
       <c r="R14" t="n">
-        <v>6515644</v>
+        <v>6515610</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2068,53 +1953,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120683514</v>
+        <v>131733192</v>
       </c>
       <c r="B15" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563290</v>
+        <v>563407</v>
       </c>
       <c r="R15" t="n">
-        <v>6515611</v>
+        <v>6515612</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,12 +2018,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I hänsyn. Större kuddar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,27 +2043,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120683683</v>
+        <v>120835744</v>
       </c>
       <c r="B16" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,21 +2070,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,10 +2094,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563407</v>
+        <v>563520</v>
       </c>
       <c r="R16" t="n">
-        <v>6515610</v>
+        <v>6515747</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2240,12 +2124,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,15 +2156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120683046</v>
+        <v>120894448</v>
       </c>
       <c r="B17" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,34 +2167,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563434</v>
+        <v>563018</v>
       </c>
       <c r="R17" t="n">
-        <v>6515522</v>
+        <v>6515323</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2342,12 +2221,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2374,15 +2253,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120682850</v>
+        <v>131732852</v>
       </c>
       <c r="B18" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,37 +2264,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563454</v>
+        <v>563493</v>
       </c>
       <c r="R18" t="n">
-        <v>6515486</v>
+        <v>6515767</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2444,12 +2318,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,65 +2338,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120683937</v>
+        <v>131732854</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563452</v>
+        <v>563365</v>
       </c>
       <c r="R19" t="n">
-        <v>6515685</v>
+        <v>6515579</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2546,12 +2419,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,27 +2439,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120684818</v>
+        <v>105315302</v>
       </c>
       <c r="B20" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,37 +2466,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563414</v>
+        <v>563015</v>
       </c>
       <c r="R20" t="n">
-        <v>6515454</v>
+        <v>6515290</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2648,12 +2520,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2664,31 +2536,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120683461</v>
+        <v>120702924</v>
       </c>
       <c r="B21" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2696,37 +2568,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenstugan VNV 1300 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563304</v>
+        <v>563538</v>
       </c>
       <c r="R21" t="n">
-        <v>6515593</v>
+        <v>6515761</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2750,12 +2625,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2764,33 +2639,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120683806</v>
+        <v>120746532</v>
       </c>
       <c r="B22" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2798,37 +2674,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563441</v>
+        <v>563407</v>
       </c>
       <c r="R22" t="n">
-        <v>6515606</v>
+        <v>6515449</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2852,12 +2731,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2866,33 +2745,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120683922</v>
+        <v>120835487</v>
       </c>
       <c r="B23" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,21 +2775,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2924,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563452</v>
+        <v>563532</v>
       </c>
       <c r="R23" t="n">
-        <v>6515685</v>
+        <v>6515728</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2954,12 +2829,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2986,15 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120683502</v>
+        <v>92007210</v>
       </c>
       <c r="B24" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3002,37 +2872,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563290</v>
+        <v>563392</v>
       </c>
       <c r="R24" t="n">
-        <v>6515611</v>
+        <v>6515438</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,12 +2929,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3070,71 +2943,71 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120683386</v>
+        <v>92007204</v>
       </c>
       <c r="B25" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563326</v>
+        <v>563509</v>
       </c>
       <c r="R25" t="n">
-        <v>6515569</v>
+        <v>6515418</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3158,12 +3031,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,27 +3051,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120682883</v>
+        <v>92007211</v>
       </c>
       <c r="B26" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,17 +3098,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563454</v>
+        <v>563448</v>
       </c>
       <c r="R26" t="n">
-        <v>6515486</v>
+        <v>6515470</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3260,12 +3132,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,27 +3152,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120683130</v>
+        <v>120682883</v>
       </c>
       <c r="B27" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,21 +3179,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,13 +3203,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563405</v>
+        <v>563454</v>
       </c>
       <c r="R27" t="n">
-        <v>6515541</v>
+        <v>6515486</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3394,15 +3265,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120684689</v>
+        <v>120683461</v>
       </c>
       <c r="B28" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,21 +3276,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3434,13 +3300,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563387</v>
+        <v>563304</v>
       </c>
       <c r="R28" t="n">
-        <v>6515509</v>
+        <v>6515593</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3496,15 +3362,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120702924</v>
+        <v>120684818</v>
       </c>
       <c r="B29" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,40 +3373,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stenstugan VNV 1300 m, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563538</v>
+        <v>563414</v>
       </c>
       <c r="R29" t="n">
-        <v>6515761</v>
+        <v>6515454</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,12 +3427,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3583,39 +3441,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120746532</v>
+        <v>120835770</v>
       </c>
       <c r="B30" t="n">
-        <v>90702</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,40 +3470,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563407</v>
+        <v>563522</v>
       </c>
       <c r="R30" t="n">
-        <v>6515449</v>
+        <v>6515762</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3680,12 +3524,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3694,7 +3538,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3713,53 +3556,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120835744</v>
+        <v>120835815</v>
       </c>
       <c r="B31" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563520</v>
+        <v>563484</v>
       </c>
       <c r="R31" t="n">
-        <v>6515747</v>
+        <v>6515764</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3803,27 +3641,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120835473</v>
+        <v>120836502</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,37 +3664,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563532</v>
+        <v>563345</v>
       </c>
       <c r="R32" t="n">
-        <v>6515728</v>
+        <v>6515843</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3905,27 +3738,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120836018</v>
+        <v>97569033</v>
       </c>
       <c r="B33" t="n">
-        <v>92008</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3933,34 +3761,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563484</v>
+        <v>563412</v>
       </c>
       <c r="R33" t="n">
-        <v>6515764</v>
+        <v>6515688</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3987,12 +3815,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4007,65 +3835,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Elin Håkansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120836109</v>
+        <v>105311995</v>
       </c>
       <c r="B34" t="n">
-        <v>94747</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563408</v>
+        <v>563411</v>
       </c>
       <c r="R34" t="n">
-        <v>6515763</v>
+        <v>6515606</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4089,12 +3912,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4105,31 +3928,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120835611</v>
+        <v>120682648</v>
       </c>
       <c r="B35" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,37 +3960,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563522</v>
+        <v>563490</v>
       </c>
       <c r="R35" t="n">
-        <v>6515762</v>
+        <v>6515454</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4191,12 +4014,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4211,27 +4034,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120835774</v>
+        <v>120682748</v>
       </c>
       <c r="B36" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4239,21 +4057,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4263,10 +4081,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563520</v>
+        <v>563472</v>
       </c>
       <c r="R36" t="n">
-        <v>6515747</v>
+        <v>6515480</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4293,12 +4111,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4325,15 +4143,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120836006</v>
+        <v>120682803</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,14 +4174,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563357</v>
+        <v>563454</v>
       </c>
       <c r="R37" t="n">
-        <v>6515821</v>
+        <v>6515486</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4395,12 +4208,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4427,15 +4240,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120835609</v>
+        <v>120683056</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,17 +4271,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563522</v>
+        <v>563434</v>
       </c>
       <c r="R38" t="n">
-        <v>6515762</v>
+        <v>6515522</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4497,12 +4305,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4517,27 +4325,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120836410</v>
+        <v>120683130</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,17 +4368,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563390</v>
+        <v>563405</v>
       </c>
       <c r="R39" t="n">
-        <v>6515758</v>
+        <v>6515541</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4599,12 +4402,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4631,15 +4434,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120835770</v>
+        <v>120683486</v>
       </c>
       <c r="B40" t="n">
-        <v>92008</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4647,37 +4445,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563522</v>
+        <v>563290</v>
       </c>
       <c r="R40" t="n">
-        <v>6515762</v>
+        <v>6515611</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4701,12 +4499,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4721,27 +4519,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120835860</v>
+        <v>120683599</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4769,17 +4562,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563423</v>
+        <v>563349</v>
       </c>
       <c r="R41" t="n">
-        <v>6515833</v>
+        <v>6515633</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,12 +4596,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,15 +4628,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120835487</v>
+        <v>120683635</v>
       </c>
       <c r="B42" t="n">
-        <v>90717</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,21 +4639,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4875,10 +4663,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563532</v>
+        <v>563407</v>
       </c>
       <c r="R42" t="n">
-        <v>6515728</v>
+        <v>6515610</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -4905,12 +4693,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4937,15 +4725,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120836502</v>
+        <v>120683806</v>
       </c>
       <c r="B43" t="n">
-        <v>92008</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4953,37 +4736,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563345</v>
+        <v>563441</v>
       </c>
       <c r="R43" t="n">
-        <v>6515843</v>
+        <v>6515606</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5007,12 +4790,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5027,27 +4810,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120836116</v>
+        <v>120683838</v>
       </c>
       <c r="B44" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5055,21 +4833,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5079,10 +4857,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563408</v>
+        <v>563506</v>
       </c>
       <c r="R44" t="n">
-        <v>6515763</v>
+        <v>6515644</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5109,12 +4887,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5141,53 +4919,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120835614</v>
+        <v>120683991</v>
       </c>
       <c r="B45" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563522</v>
+        <v>563452</v>
       </c>
       <c r="R45" t="n">
-        <v>6515762</v>
+        <v>6515685</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5211,12 +4984,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5231,49 +5004,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120835916</v>
+        <v>120684460</v>
       </c>
       <c r="B46" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5283,10 +5051,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563423</v>
+        <v>563462</v>
       </c>
       <c r="R46" t="n">
-        <v>6515833</v>
+        <v>6515641</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5313,12 +5081,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5345,15 +5113,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120835808</v>
+        <v>120684689</v>
       </c>
       <c r="B47" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5381,17 +5144,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Djupadalskärret, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563484</v>
+        <v>563387</v>
       </c>
       <c r="R47" t="n">
-        <v>6515764</v>
+        <v>6515509</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5415,12 +5178,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5435,27 +5198,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120836503</v>
+        <v>120835473</v>
       </c>
       <c r="B48" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5483,14 +5241,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563342</v>
+        <v>563532</v>
       </c>
       <c r="R48" t="n">
-        <v>6515842</v>
+        <v>6515728</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5549,15 +5307,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120895554</v>
+        <v>120835609</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5585,17 +5338,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563179</v>
+        <v>563522</v>
       </c>
       <c r="R49" t="n">
-        <v>6515532</v>
+        <v>6515762</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5619,12 +5372,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5639,27 +5392,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120893999</v>
+        <v>120835808</v>
       </c>
       <c r="B50" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5687,17 +5435,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563068</v>
+        <v>563484</v>
       </c>
       <c r="R50" t="n">
-        <v>6515304</v>
+        <v>6515764</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5721,12 +5469,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5741,27 +5489,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120895747</v>
+        <v>120835860</v>
       </c>
       <c r="B51" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5789,14 +5532,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563272</v>
+        <v>563423</v>
       </c>
       <c r="R51" t="n">
-        <v>6515573</v>
+        <v>6515833</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5823,12 +5566,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5855,15 +5598,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120893893</v>
+        <v>120836006</v>
       </c>
       <c r="B52" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5891,14 +5629,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563080</v>
+        <v>563357</v>
       </c>
       <c r="R52" t="n">
-        <v>6515376</v>
+        <v>6515821</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -5925,12 +5663,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5957,55 +5695,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120896019</v>
+        <v>120836410</v>
       </c>
       <c r="B53" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563374</v>
+        <v>563390</v>
       </c>
       <c r="R53" t="n">
-        <v>6515412</v>
+        <v>6515758</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6032,12 +5760,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6064,15 +5792,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120893971</v>
+        <v>120836503</v>
       </c>
       <c r="B54" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6100,14 +5823,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563064</v>
+        <v>563342</v>
       </c>
       <c r="R54" t="n">
-        <v>6515295</v>
+        <v>6515842</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6134,12 +5857,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6166,15 +5889,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120894013</v>
+        <v>120893893</v>
       </c>
       <c r="B55" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6182,21 +5900,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6206,10 +5924,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563039</v>
+        <v>563080</v>
       </c>
       <c r="R55" t="n">
-        <v>6515310</v>
+        <v>6515376</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6268,15 +5986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120895700</v>
+        <v>120893971</v>
       </c>
       <c r="B56" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6304,14 +6017,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långåsarna, Långåsarna, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563209</v>
+        <v>563064</v>
       </c>
       <c r="R56" t="n">
-        <v>6515543</v>
+        <v>6515295</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6370,37 +6083,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120893921</v>
+        <v>120893985</v>
       </c>
       <c r="B57" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6410,13 +6118,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563089</v>
+        <v>563068</v>
       </c>
       <c r="R57" t="n">
-        <v>6515313</v>
+        <v>6515304</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6472,48 +6180,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131740615</v>
+        <v>120894515</v>
       </c>
       <c r="B58" t="n">
-        <v>5199</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>563087</v>
+        <v>563043</v>
       </c>
       <c r="R58" t="n">
-        <v>6515384</v>
+        <v>6515437</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6537,17 +6245,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Klenare granlåga</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6562,26 +6265,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131739161</v>
+        <v>120895554</v>
       </c>
       <c r="B59" t="n">
-        <v>79936</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6609,17 +6308,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>563295</v>
+        <v>563179</v>
       </c>
       <c r="R59" t="n">
-        <v>6515614</v>
+        <v>6515532</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6643,12 +6342,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6663,26 +6362,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131732595</v>
+        <v>120895700</v>
       </c>
       <c r="B60" t="n">
-        <v>78983</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6690,37 +6385,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563194</v>
+        <v>563209</v>
       </c>
       <c r="R60" t="n">
-        <v>6515482</v>
+        <v>6515543</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6744,12 +6439,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6764,26 +6459,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739160</v>
+        <v>120895747</v>
       </c>
       <c r="B61" t="n">
-        <v>79936</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6811,17 +6502,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563430</v>
+        <v>563272</v>
       </c>
       <c r="R61" t="n">
-        <v>6515631</v>
+        <v>6515573</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6845,17 +6536,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Tallstubbe äldre</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6870,61 +6556,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737947</v>
+        <v>131739158</v>
       </c>
       <c r="B62" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Sydost, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563453</v>
+        <v>563359</v>
       </c>
       <c r="R62" t="n">
-        <v>6515693</v>
+        <v>6515817</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6987,45 +6669,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737948</v>
+        <v>131739159</v>
       </c>
       <c r="B63" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563371</v>
+        <v>563405</v>
       </c>
       <c r="R63" t="n">
-        <v>6515533</v>
+        <v>6515760</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7058,11 +6740,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7093,45 +6770,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737951</v>
+        <v>131739160</v>
       </c>
       <c r="B64" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Djupadalskärret Nordost, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563084</v>
+        <v>563430</v>
       </c>
       <c r="R64" t="n">
-        <v>6515314</v>
+        <v>6515631</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7168,7 +6845,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Relativt färska i tallåga</t>
+          <t>Tallstubbe äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7199,10 +6876,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131739165</v>
+        <v>131739161</v>
       </c>
       <c r="B65" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7230,14 +6907,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563099</v>
+        <v>563295</v>
       </c>
       <c r="R65" t="n">
-        <v>6515316</v>
+        <v>6515614</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7270,11 +6947,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,45 +6977,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131733192</v>
+        <v>131739162</v>
       </c>
       <c r="B66" t="n">
-        <v>96688</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Långåsarna Öst, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563407</v>
+        <v>563176</v>
       </c>
       <c r="R66" t="n">
-        <v>6515612</v>
+        <v>6515462</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7052,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>I hänsyn. Större kuddar.</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,10 +7083,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131732596</v>
+        <v>131739163</v>
       </c>
       <c r="B67" t="n">
-        <v>78983</v>
+        <v>79992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7094,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7118,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563156</v>
+        <v>563123</v>
       </c>
       <c r="R67" t="n">
-        <v>6515417</v>
+        <v>6515409</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,11 +7154,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7517,10 +7184,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131732593</v>
+        <v>131739164</v>
       </c>
       <c r="B68" t="n">
-        <v>78983</v>
+        <v>79992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7528,34 +7195,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>563411</v>
+        <v>563123</v>
       </c>
       <c r="R68" t="n">
-        <v>6515751</v>
+        <v>6515351</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7588,6 +7255,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gammal ihålig avverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7618,45 +7290,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131732852</v>
+        <v>131739165</v>
       </c>
       <c r="B69" t="n">
-        <v>93180</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563493</v>
+        <v>563099</v>
       </c>
       <c r="R69" t="n">
-        <v>6515767</v>
+        <v>6515316</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7689,6 +7361,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Död ved av tall under ledning</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7719,45 +7396,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131732854</v>
+        <v>131739166</v>
       </c>
       <c r="B70" t="n">
-        <v>93180</v>
+        <v>79992</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563365</v>
+        <v>563082</v>
       </c>
       <c r="R70" t="n">
-        <v>6515579</v>
+        <v>6515367</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7790,6 +7467,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På lump</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7820,10 +7502,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131739159</v>
+        <v>97569053</v>
       </c>
       <c r="B71" t="n">
-        <v>79936</v>
+        <v>4995</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7831,34 +7513,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100515</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronspraktbagge</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Buprestis haemorrhoidalis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Herbst, 1780</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupadalskärret Nordost, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>563405</v>
+        <v>563274</v>
       </c>
       <c r="R71" t="n">
-        <v>6515760</v>
+        <v>6515547</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,12 +7567,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7905,64 +7587,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Elin Håkansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739158</v>
+        <v>120894436</v>
       </c>
       <c r="B72" t="n">
-        <v>79936</v>
+        <v>5179</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långåsarna Sydost, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563359</v>
+        <v>563015</v>
       </c>
       <c r="R72" t="n">
-        <v>6515817</v>
+        <v>6515323</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7986,12 +7669,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8006,64 +7689,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131739166</v>
+        <v>120896019</v>
       </c>
       <c r="B73" t="n">
-        <v>79936</v>
+        <v>5179</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>563082</v>
+        <v>563374</v>
       </c>
       <c r="R73" t="n">
-        <v>6515367</v>
+        <v>6515412</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8087,17 +7771,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På lump</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8112,61 +7791,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739164</v>
+        <v>92005787</v>
       </c>
       <c r="B74" t="n">
-        <v>79936</v>
+        <v>58327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>563123</v>
+        <v>563533</v>
       </c>
       <c r="R74" t="n">
-        <v>6515351</v>
+        <v>6515430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8193,17 +7876,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Gammal ihålig avverkningsstubbe av tall</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8218,61 +7896,69 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Holmen</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739162</v>
+        <v>92005790</v>
       </c>
       <c r="B75" t="n">
-        <v>79936</v>
+        <v>58327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>563176</v>
+        <v>563468</v>
       </c>
       <c r="R75" t="n">
-        <v>6515462</v>
+        <v>6515487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,17 +7985,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8324,26 +8005,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Holmen</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737950</v>
+        <v>131740615</v>
       </c>
       <c r="B76" t="n">
-        <v>8455</v>
+        <v>5201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8351,34 +8032,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Stenkullen Syd, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563288</v>
+        <v>563087</v>
       </c>
       <c r="R76" t="n">
-        <v>6515549</v>
+        <v>6515384</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8415,7 +8096,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Klenare granlåga</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8446,48 +8127,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131739163</v>
+        <v>120683386</v>
       </c>
       <c r="B77" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stenkullen Syd, Ög</t>
+          <t>Långåsarna, Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563123</v>
+        <v>563326</v>
       </c>
       <c r="R77" t="n">
-        <v>6515409</v>
+        <v>6515569</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8511,12 +8192,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8531,23 +8212,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737949</v>
+        <v>120683937</v>
       </c>
       <c r="B78" t="n">
         <v>8455</v>
@@ -8578,17 +8255,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långåsarna Öst, Ög</t>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563333</v>
+        <v>563452</v>
       </c>
       <c r="R78" t="n">
-        <v>6515510</v>
+        <v>6515685</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8612,12 +8289,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8632,15 +8309,919 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120835614</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Djupadalskärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>563522</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6515762</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120835916</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Djupadalskärret, Djupadalskärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>563423</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6515833</v>
+      </c>
+      <c r="S80" t="n">
+        <v>4</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120893812</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Långåsarna, Långåsarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>563211</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6515472</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120893921</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>563089</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6515313</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131737947</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Djupadalskärret Nordost, Ög</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>563453</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6515693</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AX83" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr">
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131737948</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>563371</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6515533</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131737949</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>563333</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6515510</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131737950</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Långåsarna Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>563288</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6515549</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131737951</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stenkullen Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>563084</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6515314</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Relativt färska i tallåga</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 45701-2024 artfynd.xlsx
+++ b/artfynd/A 45701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682796</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683502</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683922</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835611</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835774</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894013</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732595</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,6 +1811,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732596</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1853,6 +1913,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836109</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683660</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733192</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835744</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2250,6 +2330,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894448</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732852</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732854</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315302</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2660,6 +2760,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120702924</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2761,6 +2866,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746532</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835487</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92007210</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3064,6 +3184,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92007204</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3165,6 +3290,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92007211</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682883</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3359,6 +3494,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683461</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3456,6 +3596,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120684818</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3553,6 +3698,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835770</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3650,6 +3800,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835815</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3747,6 +3902,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836502</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3844,6 +4004,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97569033</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3946,6 +4111,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311995</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4043,6 +4213,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682648</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4140,6 +4315,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682748</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4237,6 +4417,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682803</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4334,6 +4519,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683056</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4431,6 +4621,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683130</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4528,6 +4723,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683486</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4625,6 +4825,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683599</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4722,6 +4927,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683635</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4819,6 +5029,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683806</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4916,6 +5131,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683838</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5013,6 +5233,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683991</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5110,6 +5335,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120684460</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5207,6 +5437,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120684689</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5304,6 +5539,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835473</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5401,6 +5641,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835609</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5498,6 +5743,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835808</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5595,6 +5845,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835860</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5692,6 +5947,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836006</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5789,6 +6049,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836410</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5886,6 +6151,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836503</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5983,6 +6253,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120893893</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6080,6 +6355,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120893971</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6177,6 +6457,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120893985</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6274,6 +6559,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894515</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6371,6 +6661,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120895554</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6468,6 +6763,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120895700</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6565,6 +6865,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120895747</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6666,6 +6971,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739158</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6767,6 +7077,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739159</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6873,6 +7188,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739160</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6974,6 +7294,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739161</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7080,6 +7405,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739162</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7181,6 +7511,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739163</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7287,6 +7622,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739164</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7393,6 +7733,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739165</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7499,6 +7844,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739166</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7596,6 +7946,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97569053</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7698,6 +8053,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894436</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7800,6 +8160,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120896019</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7909,6 +8274,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005787</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8018,6 +8388,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005790</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8124,6 +8499,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740615</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8221,6 +8601,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683386</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8318,6 +8703,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683937</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8415,6 +8805,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835614</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8512,6 +8907,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120835916</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8609,6 +9009,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120893812</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8706,6 +9111,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120893921</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8807,6 +9217,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737947</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8913,6 +9328,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737948</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9014,6 +9434,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737949</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9120,6 +9545,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737950</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9226,8 +9656,101 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>